--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129770256</v>
+        <v>129769654</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,6 +833,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -844,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512478</v>
+        <v>512500</v>
       </c>
       <c r="R3" t="n">
-        <v>6294753</v>
+        <v>6294935</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129770259</v>
+        <v>129770256</v>
       </c>
       <c r="B4" t="n">
-        <v>58413</v>
+        <v>58106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,16 +936,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,12 +955,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512470</v>
+        <v>512478</v>
       </c>
       <c r="R4" t="n">
-        <v>6294734</v>
+        <v>6294753</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1045,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769654</v>
+        <v>129770259</v>
       </c>
       <c r="B5" t="n">
         <v>58413</v>
@@ -1070,17 +1075,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512500</v>
+        <v>512470</v>
       </c>
       <c r="R5" t="n">
-        <v>6294935</v>
+        <v>6294734</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129769654</v>
+        <v>129770256</v>
       </c>
       <c r="B3" t="n">
-        <v>58413</v>
+        <v>58106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,11 +833,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -849,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512500</v>
+        <v>512478</v>
       </c>
       <c r="R3" t="n">
-        <v>6294935</v>
+        <v>6294753</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129770256</v>
+        <v>129770259</v>
       </c>
       <c r="B4" t="n">
-        <v>58106</v>
+        <v>58413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,12 +950,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512478</v>
+        <v>512470</v>
       </c>
       <c r="R4" t="n">
-        <v>6294753</v>
+        <v>6294734</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129770259</v>
+        <v>129769654</v>
       </c>
       <c r="B5" t="n">
         <v>58413</v>
@@ -1075,12 +1070,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512470</v>
+        <v>512500</v>
       </c>
       <c r="R5" t="n">
-        <v>6294734</v>
+        <v>6294935</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -1165,27 +1165,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769887</v>
+        <v>129769207</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>58106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1195,12 +1195,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1214,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512423</v>
+        <v>512428</v>
       </c>
       <c r="R6" t="n">
-        <v>6294719</v>
+        <v>6294868</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1244,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,7 +1279,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Finndin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1285,27 +1290,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769207</v>
+        <v>129769887</v>
       </c>
       <c r="B7" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1315,17 +1320,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512428</v>
+        <v>512423</v>
       </c>
       <c r="R7" t="n">
-        <v>6294868</v>
+        <v>6294719</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Mattias Finndin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129770256</v>
+        <v>129770259</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512478</v>
+        <v>512470</v>
       </c>
       <c r="R3" t="n">
-        <v>6294753</v>
+        <v>6294734</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129770259</v>
+        <v>129769654</v>
       </c>
       <c r="B4" t="n">
         <v>58413</v>
@@ -950,12 +950,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512470</v>
+        <v>512500</v>
       </c>
       <c r="R4" t="n">
-        <v>6294734</v>
+        <v>6294935</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1040,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769654</v>
+        <v>129770256</v>
       </c>
       <c r="B5" t="n">
-        <v>58413</v>
+        <v>58106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1056,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,11 +1078,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512500</v>
+        <v>512478</v>
       </c>
       <c r="R5" t="n">
-        <v>6294935</v>
+        <v>6294753</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1165,27 +1165,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769207</v>
+        <v>129769887</v>
       </c>
       <c r="B6" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1195,17 +1195,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1214,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512428</v>
+        <v>512423</v>
       </c>
       <c r="R6" t="n">
-        <v>6294868</v>
+        <v>6294719</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,22 +1239,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,7 +1274,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Mattias Finndin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1290,27 +1285,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769887</v>
+        <v>129769207</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>58106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1320,12 +1315,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512423</v>
+        <v>512428</v>
       </c>
       <c r="R7" t="n">
-        <v>6294719</v>
+        <v>6294868</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Finndin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129770259</v>
+        <v>129770256</v>
       </c>
       <c r="B3" t="n">
-        <v>58413</v>
+        <v>58106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512470</v>
+        <v>512478</v>
       </c>
       <c r="R3" t="n">
-        <v>6294734</v>
+        <v>6294753</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129769654</v>
+        <v>129770259</v>
       </c>
       <c r="B4" t="n">
         <v>58413</v>
@@ -950,17 +950,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512500</v>
+        <v>512470</v>
       </c>
       <c r="R4" t="n">
-        <v>6294935</v>
+        <v>6294734</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129770256</v>
+        <v>129769654</v>
       </c>
       <c r="B5" t="n">
-        <v>58106</v>
+        <v>58413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,6 +1073,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512478</v>
+        <v>512500</v>
       </c>
       <c r="R5" t="n">
-        <v>6294753</v>
+        <v>6294935</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129770256</v>
+        <v>129770259</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512478</v>
+        <v>512470</v>
       </c>
       <c r="R3" t="n">
-        <v>6294753</v>
+        <v>6294734</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129770259</v>
+        <v>129769654</v>
       </c>
       <c r="B4" t="n">
         <v>58413</v>
@@ -950,12 +950,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512470</v>
+        <v>512500</v>
       </c>
       <c r="R4" t="n">
-        <v>6294734</v>
+        <v>6294935</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1040,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769654</v>
+        <v>129770256</v>
       </c>
       <c r="B5" t="n">
-        <v>58413</v>
+        <v>58106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1056,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,11 +1078,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512500</v>
+        <v>512478</v>
       </c>
       <c r="R5" t="n">
-        <v>6294935</v>
+        <v>6294753</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1165,27 +1165,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769887</v>
+        <v>129769207</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>58106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1195,12 +1195,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1214,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512423</v>
+        <v>512428</v>
       </c>
       <c r="R6" t="n">
-        <v>6294719</v>
+        <v>6294868</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1244,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,7 +1279,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Finndin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1285,27 +1290,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769207</v>
+        <v>129769887</v>
       </c>
       <c r="B7" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1315,17 +1320,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512428</v>
+        <v>512423</v>
       </c>
       <c r="R7" t="n">
-        <v>6294868</v>
+        <v>6294719</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Mattias Finndin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -1165,27 +1165,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769207</v>
+        <v>129769887</v>
       </c>
       <c r="B6" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1195,17 +1195,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1214,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512428</v>
+        <v>512423</v>
       </c>
       <c r="R6" t="n">
-        <v>6294868</v>
+        <v>6294719</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,22 +1239,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,7 +1274,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Mattias Finndin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1290,27 +1285,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769887</v>
+        <v>129769207</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>58106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1320,12 +1315,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512423</v>
+        <v>512428</v>
       </c>
       <c r="R7" t="n">
-        <v>6294719</v>
+        <v>6294868</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Finndin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129770256</v>
+        <v>129770259</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512478</v>
+        <v>512470</v>
       </c>
       <c r="R3" t="n">
-        <v>6294753</v>
+        <v>6294734</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129770259</v>
+        <v>129769654</v>
       </c>
       <c r="B4" t="n">
         <v>58413</v>
@@ -950,12 +950,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512470</v>
+        <v>512500</v>
       </c>
       <c r="R4" t="n">
-        <v>6294734</v>
+        <v>6294935</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1040,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769654</v>
+        <v>129770256</v>
       </c>
       <c r="B5" t="n">
-        <v>58413</v>
+        <v>58106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1056,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,11 +1078,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512500</v>
+        <v>512478</v>
       </c>
       <c r="R5" t="n">
-        <v>6294935</v>
+        <v>6294753</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769209</v>
       </c>
       <c r="B2" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>129770259</v>
       </c>
       <c r="B3" t="n">
-        <v>58413</v>
+        <v>58416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129769654</v>
+        <v>129770256</v>
       </c>
       <c r="B4" t="n">
-        <v>58413</v>
+        <v>58108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -953,11 +953,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -969,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512500</v>
+        <v>512478</v>
       </c>
       <c r="R4" t="n">
-        <v>6294935</v>
+        <v>6294753</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129770256</v>
+        <v>129769654</v>
       </c>
       <c r="B5" t="n">
-        <v>58106</v>
+        <v>58416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,6 +1073,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512478</v>
+        <v>512500</v>
       </c>
       <c r="R5" t="n">
-        <v>6294753</v>
+        <v>6294935</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1168,7 +1168,7 @@
         <v>129769887</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>129769207</v>
       </c>
       <c r="B7" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>129769651</v>
       </c>
       <c r="B8" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>129769892</v>
       </c>
       <c r="B9" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129769958</v>
       </c>
       <c r="B10" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129770259</v>
+        <v>129770256</v>
       </c>
       <c r="B3" t="n">
-        <v>58416</v>
+        <v>58108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512470</v>
+        <v>512478</v>
       </c>
       <c r="R3" t="n">
-        <v>6294734</v>
+        <v>6294753</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129770256</v>
+        <v>129770259</v>
       </c>
       <c r="B4" t="n">
-        <v>58108</v>
+        <v>58416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,12 +950,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512478</v>
+        <v>512470</v>
       </c>
       <c r="R4" t="n">
-        <v>6294753</v>
+        <v>6294734</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1165,27 +1165,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769887</v>
+        <v>129769207</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>58108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1195,12 +1195,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1214,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512423</v>
+        <v>512428</v>
       </c>
       <c r="R6" t="n">
-        <v>6294719</v>
+        <v>6294868</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1244,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,7 +1279,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Finndin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1285,27 +1290,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769207</v>
+        <v>129769887</v>
       </c>
       <c r="B7" t="n">
-        <v>58108</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1315,17 +1320,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512428</v>
+        <v>512423</v>
       </c>
       <c r="R7" t="n">
-        <v>6294868</v>
+        <v>6294719</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Mattias Finndin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129770256</v>
+        <v>129769654</v>
       </c>
       <c r="B3" t="n">
-        <v>58108</v>
+        <v>58416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,6 +833,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -844,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512478</v>
+        <v>512500</v>
       </c>
       <c r="R3" t="n">
-        <v>6294753</v>
+        <v>6294935</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129770259</v>
+        <v>129770256</v>
       </c>
       <c r="B4" t="n">
-        <v>58416</v>
+        <v>58108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,16 +936,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,12 +955,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512470</v>
+        <v>512478</v>
       </c>
       <c r="R4" t="n">
-        <v>6294734</v>
+        <v>6294753</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1045,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769654</v>
+        <v>129770259</v>
       </c>
       <c r="B5" t="n">
         <v>58416</v>
@@ -1070,17 +1075,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512500</v>
+        <v>512470</v>
       </c>
       <c r="R5" t="n">
-        <v>6294935</v>
+        <v>6294734</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769209</v>
       </c>
       <c r="B2" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129769654</v>
+        <v>129770256</v>
       </c>
       <c r="B3" t="n">
-        <v>58416</v>
+        <v>58111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,11 +833,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -849,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512500</v>
+        <v>512478</v>
       </c>
       <c r="R3" t="n">
-        <v>6294935</v>
+        <v>6294753</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129770256</v>
+        <v>129770259</v>
       </c>
       <c r="B4" t="n">
-        <v>58108</v>
+        <v>58419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,12 +950,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512478</v>
+        <v>512470</v>
       </c>
       <c r="R4" t="n">
-        <v>6294753</v>
+        <v>6294734</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129770259</v>
+        <v>129769654</v>
       </c>
       <c r="B5" t="n">
-        <v>58416</v>
+        <v>58419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,12 +1070,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512470</v>
+        <v>512500</v>
       </c>
       <c r="R5" t="n">
-        <v>6294734</v>
+        <v>6294935</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1165,27 +1165,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769207</v>
+        <v>129769887</v>
       </c>
       <c r="B6" t="n">
-        <v>58108</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1195,17 +1195,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1214,13 +1209,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512428</v>
+        <v>512423</v>
       </c>
       <c r="R6" t="n">
-        <v>6294868</v>
+        <v>6294719</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,22 +1239,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,7 +1274,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Mattias Finndin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1290,27 +1285,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769887</v>
+        <v>129769207</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>58111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1320,12 +1315,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512423</v>
+        <v>512428</v>
       </c>
       <c r="R7" t="n">
-        <v>6294719</v>
+        <v>6294868</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Finndin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1413,7 +1413,7 @@
         <v>129769651</v>
       </c>
       <c r="B8" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>129769892</v>
       </c>
       <c r="B9" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129769958</v>
       </c>
       <c r="B10" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129770256</v>
+        <v>129770259</v>
       </c>
       <c r="B3" t="n">
-        <v>58111</v>
+        <v>58419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512478</v>
+        <v>512470</v>
       </c>
       <c r="R3" t="n">
-        <v>6294753</v>
+        <v>6294734</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129770259</v>
+        <v>129769654</v>
       </c>
       <c r="B4" t="n">
         <v>58419</v>
@@ -950,12 +950,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512470</v>
+        <v>512500</v>
       </c>
       <c r="R4" t="n">
-        <v>6294734</v>
+        <v>6294935</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1040,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769654</v>
+        <v>129770256</v>
       </c>
       <c r="B5" t="n">
-        <v>58419</v>
+        <v>58111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1056,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,11 +1078,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512500</v>
+        <v>512478</v>
       </c>
       <c r="R5" t="n">
-        <v>6294935</v>
+        <v>6294753</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129770259</v>
+        <v>129770256</v>
       </c>
       <c r="B3" t="n">
-        <v>58419</v>
+        <v>58111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512470</v>
+        <v>512478</v>
       </c>
       <c r="R3" t="n">
-        <v>6294734</v>
+        <v>6294753</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129769654</v>
+        <v>129770259</v>
       </c>
       <c r="B4" t="n">
         <v>58419</v>
@@ -950,17 +950,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512500</v>
+        <v>512470</v>
       </c>
       <c r="R4" t="n">
-        <v>6294935</v>
+        <v>6294734</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129770256</v>
+        <v>129769654</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
+        <v>58419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,6 +1073,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512478</v>
+        <v>512500</v>
       </c>
       <c r="R5" t="n">
-        <v>6294753</v>
+        <v>6294935</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769209</v>
       </c>
       <c r="B2" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129770259</v>
+        <v>129770256</v>
       </c>
       <c r="B3" t="n">
-        <v>58419</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512470</v>
+        <v>512478</v>
       </c>
       <c r="R3" t="n">
-        <v>6294734</v>
+        <v>6294753</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129769654</v>
+        <v>129770259</v>
       </c>
       <c r="B4" t="n">
-        <v>58419</v>
+        <v>58420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,17 +950,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512500</v>
+        <v>512470</v>
       </c>
       <c r="R4" t="n">
-        <v>6294935</v>
+        <v>6294734</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>05:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Johan Thulin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129770256</v>
+        <v>129769654</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
+        <v>58420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,6 +1073,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512478</v>
+        <v>512500</v>
       </c>
       <c r="R5" t="n">
-        <v>6294753</v>
+        <v>6294935</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1288,7 +1288,7 @@
         <v>129769207</v>
       </c>
       <c r="B7" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>129769651</v>
       </c>
       <c r="B8" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,10 +1535,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129769892</v>
+        <v>129769958</v>
       </c>
       <c r="B9" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512377</v>
+        <v>512534</v>
       </c>
       <c r="R9" t="n">
-        <v>6294853</v>
+        <v>6294918</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1655,10 +1655,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129769958</v>
+        <v>129769892</v>
       </c>
       <c r="B10" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512534</v>
+        <v>512377</v>
       </c>
       <c r="R10" t="n">
-        <v>6294918</v>
+        <v>6294853</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129769209</v>
+        <v>129769887</v>
       </c>
       <c r="B2" t="n">
-        <v>58113</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -705,17 +705,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512512</v>
+        <v>512423</v>
       </c>
       <c r="R2" t="n">
-        <v>6294876</v>
+        <v>6294719</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Engla Grönvall</t>
+          <t>Mattias Finndin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129770256</v>
+        <v>129769198</v>
       </c>
       <c r="B3" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,6 +828,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512478</v>
+        <v>512507</v>
       </c>
       <c r="R3" t="n">
-        <v>6294753</v>
+        <v>6294987</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129770259</v>
+        <v>129769199</v>
       </c>
       <c r="B4" t="n">
-        <v>58421</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,12 +950,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +969,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512470</v>
+        <v>512496</v>
       </c>
       <c r="R4" t="n">
-        <v>6294734</v>
+        <v>6294974</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +999,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Thulin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1040,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769654</v>
+        <v>129769206</v>
       </c>
       <c r="B5" t="n">
-        <v>58421</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1056,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1089,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512500</v>
+        <v>512435</v>
       </c>
       <c r="R5" t="n">
-        <v>6294935</v>
+        <v>6294918</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1119,22 +1124,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:21</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,27 +1170,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769887</v>
+        <v>129769207</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1195,12 +1200,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1209,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512423</v>
+        <v>512428</v>
       </c>
       <c r="R6" t="n">
-        <v>6294719</v>
+        <v>6294868</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,22 +1249,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,7 +1284,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Finndin</t>
+          <t>Engla Grönvall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1285,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769207</v>
+        <v>129769209</v>
       </c>
       <c r="B7" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512428</v>
+        <v>512512</v>
       </c>
       <c r="R7" t="n">
-        <v>6294868</v>
+        <v>6294876</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1369,7 +1379,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1389,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,7 +1423,7 @@
         <v>129769651</v>
       </c>
       <c r="B8" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,7 +1548,7 @@
         <v>129769892</v>
       </c>
       <c r="B9" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1658,7 +1668,7 @@
         <v>129769958</v>
       </c>
       <c r="B10" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1768,6 +1778,851 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129769960</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lilla Ekerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>512551</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6294920</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129769964</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lilla Ekerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>512541</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6294838</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129770256</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lilla Ekerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>512478</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6294753</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Thulin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129769654</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lilla Ekerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>512500</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6294935</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>05:21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>05:21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129769896</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lilla Ekerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>512460</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6294941</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129769963</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lilla Ekerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>512541</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6294854</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129770259</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lilla Ekerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>512470</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6294734</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Thulin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
         <is>
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>

--- a/artfynd/A 52541-2025 artfynd.xlsx
+++ b/artfynd/A 52541-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769887</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769198</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1042,6 +1057,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769199</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1167,6 +1187,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769206</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1292,6 +1317,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769207</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1417,6 +1447,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769209</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1542,6 +1577,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769651</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1662,6 +1702,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769892</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1782,6 +1827,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769958</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1902,6 +1952,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769960</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2022,6 +2077,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769964</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2142,6 +2202,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129770256</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2267,6 +2332,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769654</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2387,6 +2457,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769896</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2507,6 +2582,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769963</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2627,8 +2707,31 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129770259</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>